--- a/Мазур-данные для регрессии.xlsx
+++ b/Мазур-данные для регрессии.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KL\аспиранты\Мазур\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Optimization-of-hyperparameters-of-gradient-boosting-regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF05AE6A-426A-4DF8-939F-6FF85B94BBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED17EF0-75B8-4BBC-87A0-5FD55DC43C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8495D54C-0E64-4661-8F8D-A79A4D81CAED}"/>
+    <workbookView xWindow="22932" yWindow="-6096" windowWidth="13176" windowHeight="22536" xr2:uid="{8495D54C-0E64-4661-8F8D-A79A4D81CAED}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,26 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>ув</t>
   </si>
@@ -244,11 +258,8 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve"> в верхней </t>
+      <t xml:space="preserve"> в верхней точке частотного диапазона</t>
     </r>
-  </si>
-  <si>
-    <t>точке частотного диапазона</t>
   </si>
 </sst>
 </file>
@@ -462,9 +473,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -502,7 +513,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -608,7 +619,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -750,7 +761,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -759,26 +770,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFBEAB7-E4E4-4EA6-BE26-83F0DFEDB758}">
   <dimension ref="A1:P91"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.90625" customWidth="1"/>
-    <col min="13" max="13" width="12.81640625" customWidth="1"/>
-    <col min="14" max="14" width="33.453125" customWidth="1"/>
-    <col min="16" max="16" width="13.1796875" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.85546875" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" customWidth="1"/>
+    <col min="14" max="14" width="33.42578125" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -825,7 +836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>26</v>
       </c>
@@ -873,7 +884,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>28</v>
       </c>
@@ -921,7 +932,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>25</v>
       </c>
@@ -969,7 +980,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>26</v>
       </c>
@@ -1017,7 +1028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>28</v>
       </c>
@@ -1065,7 +1076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>25</v>
       </c>
@@ -1113,7 +1124,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>23</v>
       </c>
@@ -1161,7 +1172,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="11.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>25</v>
       </c>
@@ -1209,7 +1220,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>18</v>
       </c>
@@ -1257,7 +1268,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>23</v>
       </c>
@@ -1303,7 +1314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>25</v>
       </c>
@@ -1341,11 +1352,8 @@
       <c r="N12" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="O12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>24</v>
       </c>
@@ -1381,7 +1389,7 @@
         <v>47.774836184583066</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>28</v>
       </c>
@@ -1417,7 +1425,7 @@
         <v>48.191881022717347</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>27</v>
       </c>
@@ -1453,7 +1461,7 @@
         <v>51.139433523068369</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>26</v>
       </c>
@@ -1489,7 +1497,7 @@
         <v>51.697510810246627</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>25</v>
       </c>
@@ -1525,7 +1533,7 @@
         <v>53.206255517273618</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>19</v>
       </c>
@@ -1561,7 +1569,7 @@
         <v>49.330532103693869</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>23</v>
       </c>
@@ -1597,7 +1605,7 @@
         <v>46.531424719266468</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>27</v>
       </c>
@@ -1633,7 +1641,7 @@
         <v>47.938740346464769</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>28</v>
       </c>
@@ -1669,7 +1677,7 @@
         <v>47.74523970534748</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1705,7 +1713,7 @@
         <v>47.686396523021052</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1741,7 +1749,7 @@
         <v>49.91106286840018</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>29</v>
       </c>
@@ -1777,7 +1785,7 @@
         <v>47.634279935629365</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -1813,7 +1821,7 @@
         <v>50.579919469776868</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -1849,7 +1857,7 @@
         <v>52.805083285193788</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>19</v>
       </c>
@@ -1885,7 +1893,7 @@
         <v>51.047353505200128</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>29</v>
       </c>
@@ -1921,7 +1929,7 @@
         <v>48.021894912510831</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>22</v>
       </c>
@@ -1957,7 +1965,7 @@
         <v>51.517319131962367</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>23</v>
       </c>
@@ -1993,7 +2001,7 @@
         <v>51.976858726505156</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -2029,7 +2037,7 @@
         <v>49.700367766225568</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>22</v>
       </c>
@@ -2065,7 +2073,7 @@
         <v>49.644961438048782</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>23</v>
       </c>
@@ -2101,7 +2109,7 @@
         <v>48.543060418010811</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>25</v>
       </c>
@@ -2137,7 +2145,7 @@
         <v>47.155692661554802</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>26</v>
       </c>
@@ -2173,7 +2181,7 @@
         <v>47.373034768174868</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>21</v>
       </c>
@@ -2209,7 +2217,7 @@
         <v>49.932666173410318</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>24</v>
       </c>
@@ -2245,7 +2253,7 @@
         <v>47.72296890604408</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>25</v>
       </c>
@@ -2281,7 +2289,7 @@
         <v>48.277863960075209</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>24</v>
       </c>
@@ -2317,7 +2325,7 @@
         <v>49.220685231080822</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>23</v>
       </c>
@@ -2353,7 +2361,7 @@
         <v>49.360587205091122</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>21</v>
       </c>
@@ -2389,7 +2397,7 @@
         <v>48.860566476931631</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>28</v>
       </c>
@@ -2425,7 +2433,7 @@
         <v>49.386934777220795</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>24</v>
       </c>
@@ -2461,7 +2469,7 @@
         <v>46.431725768428734</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>26</v>
       </c>
@@ -2497,7 +2505,7 @@
         <v>48.402991571324883</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>22</v>
       </c>
@@ -2533,7 +2541,7 @@
         <v>48.282193915388049</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>21</v>
       </c>
@@ -2569,7 +2577,7 @@
         <v>56.95481676490197</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>22</v>
       </c>
@@ -2605,7 +2613,7 @@
         <v>48.750612633917001</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>24</v>
       </c>
@@ -2641,7 +2649,7 @@
         <v>47.993405494535821</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>24</v>
       </c>
@@ -2677,7 +2685,7 @@
         <v>51.986570869544224</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>20</v>
       </c>
@@ -2713,7 +2721,7 @@
         <v>50.182248201061988</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>27</v>
       </c>
@@ -2749,7 +2757,7 @@
         <v>54.259687322722812</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>24</v>
       </c>
@@ -2785,7 +2793,7 @@
         <v>48.644605846358132</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>22</v>
       </c>
@@ -2821,7 +2829,7 @@
         <v>49.909203421480811</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>22</v>
       </c>
@@ -2857,7 +2865,7 @@
         <v>47.900504736833511</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>22</v>
       </c>
@@ -2893,7 +2901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>20</v>
       </c>
@@ -2929,7 +2937,7 @@
         <v>49.100948885606016</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>24</v>
       </c>
@@ -2965,7 +2973,7 @@
         <v>46.442231121714798</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>22</v>
       </c>
@@ -3001,7 +3009,7 @@
         <v>46.105057747192873</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>22</v>
       </c>
@@ -3037,7 +3045,7 @@
         <v>49.140853712934067</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>25</v>
       </c>
@@ -3073,7 +3081,7 @@
         <v>50.734289171585338</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>20</v>
       </c>
@@ -3109,7 +3117,7 @@
         <v>49.232382280757882</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>27</v>
       </c>
@@ -3145,7 +3153,7 @@
         <v>46.277285494792054</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>24</v>
       </c>
@@ -3181,7 +3189,7 @@
         <v>52.455126678141497</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>22</v>
       </c>
@@ -3217,7 +3225,7 @@
         <v>52.730012720637376</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>19</v>
       </c>
@@ -3253,7 +3261,7 @@
         <v>51.488171741890191</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>22</v>
       </c>
@@ -3289,7 +3297,7 @@
         <v>48.692317197309762</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>24</v>
       </c>
@@ -3325,7 +3333,7 @@
         <v>53.010299956639813</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>27</v>
       </c>
@@ -3361,7 +3369,7 @@
         <v>50.901766303490881</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>24</v>
       </c>
@@ -3397,7 +3405,7 @@
         <v>52.276010785054474</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>20</v>
       </c>
@@ -3433,7 +3441,7 @@
         <v>51.488171741890191</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>23</v>
       </c>
@@ -3469,7 +3477,7 @@
         <v>46.637473524536873</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>28</v>
       </c>
@@ -3505,7 +3513,7 @@
         <v>46.057985608873643</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>24</v>
       </c>
@@ -3541,7 +3549,7 @@
         <v>48.4567748570649</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>27</v>
       </c>
@@ -3577,7 +3585,7 @@
         <v>46.561175044187515</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>22</v>
       </c>
@@ -3613,7 +3621,7 @@
         <v>48.590731580075698</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>22</v>
       </c>
@@ -3649,7 +3657,7 @@
         <v>48.789563072752244</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>21</v>
       </c>
@@ -3685,7 +3693,7 @@
         <v>49.24279286061882</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>28</v>
       </c>
@@ -3721,7 +3729,7 @@
         <v>50.301947853567512</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>26</v>
       </c>
@@ -3757,7 +3765,7 @@
         <v>47.393132460148344</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>24</v>
       </c>
@@ -3793,7 +3801,7 @@
         <v>50.163904161881696</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>24</v>
       </c>
@@ -3829,7 +3837,7 @@
         <v>46.917914197088955</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>29</v>
       </c>
@@ -3865,7 +3873,7 @@
         <v>48.728952016351926</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>23</v>
       </c>
@@ -3901,7 +3909,7 @@
         <v>50.734289171585338</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>25</v>
       </c>
@@ -3937,7 +3945,7 @@
         <v>48.886340705809737</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>28</v>
       </c>
@@ -3973,7 +3981,7 @@
         <v>50.382823579657966</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>29</v>
       </c>
@@ -4009,7 +4017,7 @@
         <v>48.043866012418441</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>29</v>
       </c>
@@ -4045,7 +4053,7 @@
         <v>52.388820889151368</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>26</v>
       </c>
@@ -4081,7 +4089,7 @@
         <v>48.070494326965161</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>23</v>
       </c>
@@ -4117,7 +4125,7 @@
         <v>46.146491186359825</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>26</v>
       </c>
@@ -4153,7 +4161,7 @@
         <v>49.322482157331571</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>25</v>
       </c>
